--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
@@ -468,10 +468,10 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.01274929496088828</v>
+        <v>-0.06730848062835182</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.276140753096718</v>
+        <v>0.1628183339349606</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.1357170036449519</v>
+        <v>-0.4936048351350182</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1880082213586419</v>
+        <v>-0.6453958198073382</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2429498866923691</v>
+        <v>0.1411261378642936</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.05935040683363518</v>
+        <v>-0.5365554829929057</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>11.78225584245999</v>
+        <v>9.396930806312071</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2028348815837588</v>
+        <v>-0.2106449210350836</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2267452208490694</v>
+        <v>0.2575091802175737</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.9928067246052176</v>
+        <v>-0.8853627618428426</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.296354767923259</v>
+        <v>-1.18602128048618</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2524002198002396</v>
+        <v>0.2871402346904109</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8330716097335503</v>
+        <v>-0.7603349700542262</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>13.40328719320722</v>
+        <v>11.99344556103829</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.01476408226429482</v>
+        <v>0.1293546270796389</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2099040326525574</v>
+        <v>0.1922291011002605</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.04030372169638648</v>
+        <v>0.6772978845272256</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.05864002625193403</v>
+        <v>1.010149555505454</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1889335702249527</v>
+        <v>0.1764578829225691</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.08134846665655782</v>
+        <v>0.7653149483258664</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>13.29190183764343</v>
+        <v>13.18549842291411</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1080447569874383</v>
+        <v>0.06825658026005521</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2146519697099948</v>
+        <v>0.234664613282334</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5349910205961206</v>
+        <v>0.346117670436202</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7967109892358293</v>
+        <v>0.5068089637313872</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1522292180259817</v>
+        <v>0.1643906075309544</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.74067472509426</v>
+        <v>0.4329640375175924</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>13.88243451967313</v>
+        <v>15.97864500021941</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3981151116043784</v>
+        <v>0.4863856984696957</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2457414931972852</v>
+        <v>0.2592317024025209</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.47805352459753</v>
+        <v>1.659335527269735</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.074816594455361</v>
+        <v>2.398581727295146</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1378929159023993</v>
+        <v>0.1533876721856222</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.013764030226283</v>
+        <v>3.314256482191305</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>15.66798570305092</v>
+        <v>14.75304345182813</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.08417688348024699</v>
+        <v>0.2450211283836132</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3356274488296594</v>
+        <v>0.3606239860881418</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5596195157177187</v>
+        <v>1.240124222397492</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7910065516228918</v>
+        <v>1.859528399259807</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2190303685198477</v>
+        <v>0.1293650644378833</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7204632149250615</v>
+        <v>3.770884544676842</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>13.31433175724244</v>
+        <v>12.2034228953592</v>
       </c>
     </row>
   </sheetData>
